--- a/gm/resources/sample/loginConfig.xlsx
+++ b/gm/resources/sample/loginConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11925"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="loginConfig" sheetId="1" r:id="rId1"/>
@@ -88,7 +88,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="15">
   <si>
     <t>序号ID</t>
   </si>
@@ -123,7 +123,7 @@
     <t>google登入</t>
   </si>
   <si>
-    <t>1990000_21400</t>
+    <t>1990000_200000</t>
   </si>
   <si>
     <t>ios登入</t>
@@ -133,9 +133,6 @@
   </si>
   <si>
     <t>手机登入</t>
-  </si>
-  <si>
-    <t>1990000_85700</t>
   </si>
 </sst>
 </file>
@@ -1256,7 +1253,7 @@
         <v>14</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" s="2" customFormat="1"/>
